--- a/sources/michelle_step10.xlsx
+++ b/sources/michelle_step10.xlsx
@@ -945,11 +945,6 @@
           <t>d</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>

--- a/sources/michelle_step10.xlsx
+++ b/sources/michelle_step10.xlsx
@@ -7714,12 +7714,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Launching Shuttle [~5]</t>
+          <t>Launching Shuttle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Launching Shuttle [~5]</t>
+          <t>Launching Shuttle</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">

--- a/sources/michelle_step10.xlsx
+++ b/sources/michelle_step10.xlsx
@@ -425,7 +425,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="51" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
@@ -830,22 +830,27 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>b+2</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>b+2</t>
+          <t>1+3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arm Whip</t>
+          <t>Blizard Suplex</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arm Whip</t>
+          <t>Blizard Suplex</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -855,42 +860,37 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Special Tag Throw with Julia only. Julia finishes with a Running Bulldog. Total damage is 12,24.</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
+          <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -902,57 +902,67 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>– d+1+2</t>
+          <t>1+3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>b+2 ,d+1+2</t>
+          <t>1+3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2+4; 2+5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>– Rear Suplex</t>
+          <t>Southern Cross Suplex</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arm Whip – Rear Suplex</t>
+          <t>Southern Cross Suplex</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>12,45</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Right</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>151f3bbe-77de-4044-9738-f8670c4da698</t>
+          <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -979,12 +989,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blizard Suplex</t>
+          <t>Rear Suplex</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blizard Suplex</t>
+          <t>Rear Suplex</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -994,403 +1004,458 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>e0cf556a-57d8-4762-b577-f4d445bc558f</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>e0cf556a-57d8-4762-b577-f4d445bc558f</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Basic Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>From Stance</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Command Full</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Move Name Full</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Hits Per Move</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Speed Full</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv Full</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>Damage Full</t>
+        </is>
+      </c>
+      <c r="T11" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="U11" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range Full</t>
+        </is>
+      </c>
+      <c r="V11" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="W11" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="X11" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="Z11" s="1" t="inlineStr">
+        <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="AA11" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="AB11" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="AC11" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="AD11" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>b56b385d-5cb6-4b61-a390-be7a9104c9cf</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1+3</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1+3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2+4; 2+5</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Southern Cross Suplex</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Southern Cross Suplex</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>736d0fd3-1148-4734-be27-34a2a82b7048</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1+3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1+3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2+4; 2+5</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Rear Suplex</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rear Suplex</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Back</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>e0cf556a-57d8-4762-b577-f4d445bc558f</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Basic Arts</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>c6033170-fc6f-41ba-a03a-01b8aaf76e68</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07ce9c8f-23a9-4d57-8e2e-0b53aa195908</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>From Stance</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Command Full</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Move Name Full</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>Hits Per Move</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>Speed Full</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv Full</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="R13" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t>Damage Full</t>
-        </is>
-      </c>
-      <c r="T13" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="U13" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range Full</t>
-        </is>
-      </c>
-      <c r="V13" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="W13" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="X13" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="Y13" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="Z13" s="1" t="inlineStr">
-        <is>
-          <t>Taggable</t>
-        </is>
-      </c>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="AC13" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7ee48452-ecf0-4e47-9e91-025d60848d80</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>68e8fa5c-b7a2-4e20-a74b-c7513611726f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1405,24 +1470,24 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>c6033170-fc6f-41ba-a03a-01b8aaf76e68</t>
+          <t>a5606039-9ce1-4b7f-b85d-f6400494d9ff</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07ce9c8f-23a9-4d57-8e2e-0b53aa195908</t>
+          <t>72c31814-4f1f-4b4a-895d-98ee23de95ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1442,47 +1507,47 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1497,24 +1562,24 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>7ee48452-ecf0-4e47-9e91-025d60848d80</t>
+          <t>686545e2-829e-443e-b4c8-9afb1ab22fd1</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>68e8fa5c-b7a2-4e20-a74b-c7513611726f</t>
+          <t>323db6b0-f3e0-4fac-aa55-636e0ff56b9d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>f+1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>f+1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1524,57 +1589,57 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1589,24 +1654,24 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>a5606039-9ce1-4b7f-b85d-f6400494d9ff</t>
+          <t>003ea89d-245e-4ecf-a870-27b43aa73f51</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>72c31814-4f1f-4b4a-895d-98ee23de95ee</t>
+          <t>06c2823e-acfb-4422-9092-e8a5b2433449</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>f+2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>f+2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1626,47 +1691,47 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1681,24 +1746,24 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>686545e2-829e-443e-b4c8-9afb1ab22fd1</t>
+          <t>cbd0f936-ebdc-4a00-9b7d-ee77f15c1c41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>323db6b0-f3e0-4fac-aa55-636e0ff56b9d</t>
+          <t>9f424d4e-45d3-4e2b-a510-2bce905bcee1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>f+1</t>
+          <t>f+3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>f+1</t>
+          <t>f+3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1708,57 +1773,57 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -1773,24 +1838,24 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>003ea89d-245e-4ecf-a870-27b43aa73f51</t>
+          <t>f7d4503e-eb69-4def-bf82-52ad23e0146d</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>06c2823e-acfb-4422-9092-e8a5b2433449</t>
+          <t>98afa8e3-4411-4663-bc7d-078228b3d1d8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>f+2</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>f+2</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1810,47 +1875,47 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -1865,24 +1930,24 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>cbd0f936-ebdc-4a00-9b7d-ee77f15c1c41</t>
+          <t>24275688-5897-45e5-9139-9315f9df4062</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>9f424d4e-45d3-4e2b-a510-2bce905bcee1</t>
+          <t>ac220679-3490-4372-a7fb-7a57d3cb2ef4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>f+3</t>
+          <t>d+1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>f+3</t>
+          <t>d+1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1892,89 +1957,89 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>s</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>s</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>f7d4503e-eb69-4def-bf82-52ad23e0146d</t>
+          <t>7f5a2e81-ff5d-40c2-ba9e-f962140e37cb</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>98afa8e3-4411-4663-bc7d-078228b3d1d8</t>
+          <t>ff9207d7-f21a-43c0-b432-e8e0378ea769</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>f+4</t>
+          <t>d+2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>f+4</t>
+          <t>d+2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1994,79 +2059,79 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>s</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>s</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>24275688-5897-45e5-9139-9315f9df4062</t>
+          <t>f20c1a12-e493-4f99-ab06-70b120c75788</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>ac220679-3490-4372-a7fb-7a57d3cb2ef4</t>
+          <t>b0b03e78-02c3-4108-aa77-3af9ba1c9cdb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>d+1</t>
+          <t>d+3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>d+1</t>
+          <t>d+3</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2076,89 +2141,89 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>7f5a2e81-ff5d-40c2-ba9e-f962140e37cb</t>
+          <t>8fa2057e-0c2d-4012-94a8-1fb2fedc94cc</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>ff9207d7-f21a-43c0-b432-e8e0378ea769</t>
+          <t>0ff15731-ad31-4a6e-8b0e-6c2f6be90646</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>d+2</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>d+2</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2168,89 +2233,89 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>f20c1a12-e493-4f99-ab06-70b120c75788</t>
+          <t>d3470262-1904-4531-adf4-5a81a970055d</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>b0b03e78-02c3-4108-aa77-3af9ba1c9cdb</t>
+          <t>c181cbde-fea4-4334-a79f-506ad4c2ee7e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>d+3</t>
+          <t>FC+1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>d+3</t>
+          <t>FC+1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2260,89 +2325,89 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>s</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>s</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>8fa2057e-0c2d-4012-94a8-1fb2fedc94cc</t>
+          <t>f885b616-b303-4b52-b32d-972fd7e4b968</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0ff15731-ad31-4a6e-8b0e-6c2f6be90646</t>
+          <t>fa9aa0bc-4a3b-436e-96b4-b66c616dd1d2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>d+4</t>
+          <t>FC+2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>d+4</t>
+          <t>FC+2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2352,89 +2417,89 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>s</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>s</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>d3470262-1904-4531-adf4-5a81a970055d</t>
+          <t>7064dd06-e117-4818-8886-1da7e10b0239</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>c181cbde-fea4-4334-a79f-506ad4c2ee7e</t>
+          <t>72664919-c993-4044-ae65-0679e9da2480</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>FC+1</t>
+          <t>FC+3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FC+1</t>
+          <t>FC+3</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2444,89 +2509,89 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>f885b616-b303-4b52-b32d-972fd7e4b968</t>
+          <t>437979bc-f7aa-4448-8a71-5c942fd40369</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>fa9aa0bc-4a3b-436e-96b4-b66c616dd1d2</t>
+          <t>6d9f53d2-b02a-4008-9e3c-b2ade8c87e14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>FC+2</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FC+2</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2536,89 +2601,89 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>l</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>7064dd06-e117-4818-8886-1da7e10b0239</t>
+          <t>63d37d7e-80e3-4840-ba9c-0051bba960ff</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>72664919-c993-4044-ae65-0679e9da2480</t>
+          <t>ce93e07c-a3ea-4497-b3d1-942aeba96d92</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>FC+3</t>
+          <t>WS+1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FC+3</t>
+          <t>WS+1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2628,42 +2693,42 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2683,34 +2748,34 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>437979bc-f7aa-4448-8a71-5c942fd40369</t>
+          <t>45ce8ef0-85b9-4e4e-b2b9-3bcb73441a6a</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>6d9f53d2-b02a-4008-9e3c-b2ade8c87e14</t>
+          <t>22ce4c72-e30f-40fe-8d67-b3801ad23f3e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>FC+4</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FC+4</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2720,89 +2785,89 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>63d37d7e-80e3-4840-ba9c-0051bba960ff</t>
+          <t>76267b4b-2763-4391-97bf-83dd2c0520dd</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>ce93e07c-a3ea-4497-b3d1-942aeba96d92</t>
+          <t>46487fe7-bf44-4cad-b534-afe79efc0b70</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>WS+1</t>
+          <t>WS+3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WS+1</t>
+          <t>WS+3</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2812,89 +2877,89 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>45ce8ef0-85b9-4e4e-b2b9-3bcb73441a6a</t>
+          <t>3706c6b1-0fa1-4a1f-9f88-a60645b682d0</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>22ce4c72-e30f-40fe-8d67-b3801ad23f3e</t>
+          <t>24e073de-e439-4048-af3f-df400b03385b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>WS+2</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WS+2</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2904,42 +2969,42 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2969,24 +3034,24 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>76267b4b-2763-4391-97bf-83dd2c0520dd</t>
+          <t>a4a15337-a47f-4860-aa35-c4bde965e01b</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>46487fe7-bf44-4cad-b534-afe79efc0b70</t>
+          <t>fe59a187-8ce3-4127-80c9-5546a390b4c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>WS+3</t>
+          <t>df+1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WS+3</t>
+          <t>df+1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2996,89 +3061,89 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>3706c6b1-0fa1-4a1f-9f88-a60645b682d0</t>
+          <t>85e20006-05ae-4532-a1a8-647332d09cac</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>24e073de-e439-4048-af3f-df400b03385b</t>
+          <t>05dfb79f-79f9-4e09-8ada-db0ce4fb168c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>WS+4</t>
+          <t>df+2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WS+4</t>
+          <t>df+2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3088,57 +3153,57 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3153,24 +3218,24 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>a4a15337-a47f-4860-aa35-c4bde965e01b</t>
+          <t>42dc9699-91a5-4f0f-87ac-980938243165</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>fe59a187-8ce3-4127-80c9-5546a390b4c3</t>
+          <t>03456ef2-ec89-46af-ba68-eaf6a8c163a4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>df+1</t>
+          <t>df+3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>df+1</t>
+          <t>df+3</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3180,57 +3245,57 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3245,24 +3310,24 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>85e20006-05ae-4532-a1a8-647332d09cac</t>
+          <t>483fec58-19b9-4705-aa78-4dd3faa96ec5</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>05dfb79f-79f9-4e09-8ada-db0ce4fb168c</t>
+          <t>fe00be93-e80a-4b6c-b722-119c842f22ea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>df+2</t>
+          <t>df+4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>df+2</t>
+          <t>df+4</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3272,57 +3337,57 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3337,378 +3402,413 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>42dc9699-91a5-4f0f-87ac-980938243165</t>
+          <t>834b467d-4bf0-475e-8c25-701077632fbe</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>03456ef2-ec89-46af-ba68-eaf6a8c163a4</t>
+          <t>6de38d6f-c7c6-4e62-9eb4-e57135f82b61</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>df+3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>df+3</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Special Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>From Stance</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Command Full</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>Move Name Full</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>Hits Per Move</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>Speed Full</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv Full</t>
+        </is>
+      </c>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv Full</t>
+        </is>
+      </c>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="R38" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="S38" s="1" t="inlineStr">
+        <is>
+          <t>Damage Full</t>
+        </is>
+      </c>
+      <c r="T38" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="U38" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range Full</t>
+        </is>
+      </c>
+      <c r="V38" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="W38" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="X38" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="Y38" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="Z38" s="1" t="inlineStr">
+        <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="AA38" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="AB38" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="AC38" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="AD38" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1+2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1+2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Twin Arrow</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Twin Arrow</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>483fec58-19b9-4705-aa78-4dd3faa96ec5</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>fe00be93-e80a-4b6c-b722-119c842f22ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>df+4</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>df+4</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>834b467d-4bf0-475e-8c25-701077632fbe</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>6de38d6f-c7c6-4e62-9eb4-e57135f82b61</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Special Arts</t>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>4482f91b-86b4-4a8f-a816-db2b2f2fbd46</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>e9b6c796-c000-4ed2-8368-c690971c3c01</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>From Stance</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>Command Full</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>Move Name Full</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="H40" s="1" t="inlineStr">
-        <is>
-          <t>Hits Per Move</t>
-        </is>
-      </c>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>Speed Full</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv Full</t>
-        </is>
-      </c>
-      <c r="M40" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="N40" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="P40" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv Full</t>
-        </is>
-      </c>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="R40" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="S40" s="1" t="inlineStr">
-        <is>
-          <t>Damage Full</t>
-        </is>
-      </c>
-      <c r="T40" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="U40" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range Full</t>
-        </is>
-      </c>
-      <c r="V40" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="W40" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="X40" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="Y40" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="Z40" s="1" t="inlineStr">
-        <is>
-          <t>Taggable</t>
-        </is>
-      </c>
-      <c r="AA40" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="AB40" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="AC40" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="AD40" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>f+1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>f+1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Flash Uppercut</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Flash Uppercut</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>7bfbcd5b-ddbe-4aa7-b650-8564323234ed</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>77114bb1-2d92-497f-a701-65b23a7a3dc3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>1+2</t>
+          <t>d,df+1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1+2</t>
+          <t>d,df+1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Twin Arrow</t>
+          <t>Flash Punch</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Twin Arrow</t>
+          <t>Flash Punch</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3718,22 +3818,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3758,17 +3858,17 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -3781,178 +3881,163 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>4482f91b-86b4-4a8f-a816-db2b2f2fbd46</t>
+          <t>06464f67-c803-4f17-b171-2197c0239e6f</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>e9b6c796-c000-4ed2-8368-c690971c3c01</t>
+          <t>b7444905-de92-415b-b2fe-4a95a0cf40ea</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>f+1</t>
+          <t>1~1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>f+1</t>
+          <t>1 ~1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Flash Uppercut</t>
+          <t>G-Clef - Club Fist</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flash Uppercut</t>
+          <t>G-Clef - Club Fist</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>0 -15</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>0 -15</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6 -4</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6 -4</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6 -4</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6 -4</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
+          <t>10,5</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,5</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>hm</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Damage of the 1st punch is only 5 if the 2nd punch isn't executed.</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>7bfbcd5b-ddbe-4aa7-b650-8564323234ed</t>
+          <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>77114bb1-2d92-497f-a701-65b23a7a3dc3</t>
+          <t>319b3d6e-6130-4f50-9ab9-93ca205ab84e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>d,df+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>d,df+1</t>
+          <t>1 ~1 ,1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Flash Punch</t>
+          <t>– Flash Uppercut</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Flash Punch</t>
+          <t>G-Clef - Club Fist – Flash Uppercut</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0 -15 -14</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3962,32 +4047,32 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>+6 -4 KD</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6 -4 KD</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10,5,21</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -3997,201 +4082,216 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>06464f67-c803-4f17-b171-2197c0239e6f</t>
+          <t>d8373306-9820-4552-b536-0bed8b49a0a3</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>b7444905-de92-415b-b2fe-4a95a0cf40ea</t>
+          <t>b2044aba-d99f-4d1d-aa13-7d104d07f1bb</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>1~1</t>
+          <t>– 4,3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 ~1</t>
+          <t>1 ~1 ,4 ,3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>G-Clef - Club Fist</t>
+          <t>– Bow &amp; Arrow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>G-Clef - Club Fist</t>
+          <t>G-Clef - Club Fist – Bow &amp; Arrow</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
+          <t>1 1 1 1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0 -15</t>
+          <t>-13 -12</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0 -15</t>
+          <t>0 -15 -13 -12</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+6 -4</t>
+          <t>-2 KD</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>+6 -4</t>
+          <t>+6 -4 -2 KD</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>+6 -4</t>
+          <t>-2 KD</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>+6 -4</t>
+          <t>+6 -4 -2 KD</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>12,15</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>10,5,12,15</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>hm</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>hm</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Damage of the 1st punch is only 5 if the 2nd punch isn't executed.</t>
+          <t>hmLm</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
+          <t>db045429-faae-403f-9a70-90085ac5800d</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>a8c95e80-af11-47a1-b203-bea91b893aa3</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
           <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>319b3d6e-6130-4f50-9ab9-93ca205ab84e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>df+1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1 ~1 ,1</t>
+          <t>df+1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>– Flash Uppercut</t>
+          <t>Club Fist</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>G-Clef - Club Fist – Flash Uppercut</t>
+          <t>Club Fist</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>0 -15 -14</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>+6 -4 KD</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>+6 -4 KD</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>10,5,21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4201,258 +4301,253 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>hmm</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>m</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>d8373306-9820-4552-b536-0bed8b49a0a3</t>
+          <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>b2044aba-d99f-4d1d-aa13-7d104d07f1bb</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
+          <t>45e928fe-2dae-464b-b94d-bf1038f0acb5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>– 4,3</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 ~1 ,4 ,3</t>
+          <t>df+1 ,1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>– Bow &amp; Arrow</t>
+          <t>– Flash Uppercut</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>G-Clef - Club Fist – Bow &amp; Arrow</t>
+          <t>Club Fist – Flash Uppercut</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-13 -12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0 -15 -13 -12</t>
+          <t>-15 -14</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>+6 -4 -2 KD</t>
+          <t>-4 KD</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>+6 -4 -2 KD</t>
+          <t>-4 KD</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>12,15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10,5,12,15</t>
+          <t>8,21</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>hmLm</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>db045429-faae-403f-9a70-90085ac5800d</t>
+          <t>937031b4-16d7-4706-9af8-7c3cc587432e</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>a8c95e80-af11-47a1-b203-bea91b893aa3</t>
+          <t>969ae53c-460d-46a5-b67e-34c8fe3c2f4e</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ab733431-ae0b-47eb-b429-70ddf9a50561</t>
+          <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>df+1</t>
+          <t>– 4,3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>df+1</t>
+          <t>df+1 ,4 ,3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Fist</t>
+          <t>– Bow &amp; Arrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Fist</t>
+          <t>Club Fist – Bow &amp; Arrow</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-13 -12</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-15 -13 -12</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2 KD</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-4 -2 KD</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2 KD</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-4 -2 KD</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12,15</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8,12,15</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mLm</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
+          <t>5799327f-0f65-4b2d-a011-7a75a92eefcf</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>b1bc079d-23df-4712-a7c6-aad9b7fea595</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
           <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>45e928fe-2dae-464b-b94d-bf1038f0acb5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>df+1 ,1</t>
+          <t>1 ~2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>– Flash Uppercut</t>
+          <t>G-Clef - Gut Punch</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Fist – Flash Uppercut</t>
+          <t>G-Clef - Gut Punch</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4460,111 +4555,106 @@
           <t>1 1</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>0 -15</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-15 -14</t>
+          <t>0 -15</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6 +5</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-4 KD</t>
+          <t>+6 +5</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+6 +5</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-4 KD</t>
+          <t>+6 +5</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>hm</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Damage of the 1st punch is only 5 if the 2nd punch isn't executed.</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>937031b4-16d7-4706-9af8-7c3cc587432e</t>
+          <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>969ae53c-460d-46a5-b67e-34c8fe3c2f4e</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
+          <t>93869afa-9cfe-4d58-ac4e-9f08aa9a710d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>– 4,3</t>
+          <t>– ~1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>df+1 ,4 ,3</t>
+          <t>1 ~2 ~1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>– Bow &amp; Arrow</t>
+          <t>– Skyscraper Cannon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Club Fist – Bow &amp; Arrow</t>
+          <t>G-Clef - Gut Punch – Skyscraper Cannon</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4574,206 +4664,206 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>-13 -12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-15 -13 -12</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>-2 KD</t>
+          <t>0 -15</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>-4 -2 KD</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>-2 KD</t>
+          <t>+6 +5</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>-4 -2 KD</t>
+          <t>+6 +5</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>12,15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>8,12,15</t>
+          <t>5,8,21</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>mLm</t>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>The 3rd only occurs if the 1st hit was a counter hit. Second hit will be 15 damage.</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>5799327f-0f65-4b2d-a011-7a75a92eefcf</t>
+          <t>f0f2bfda-dfa5-40f3-ae66-b166200ab547</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>b1bc079d-23df-4712-a7c6-aad9b7fea595</t>
+          <t>5748a150-d4fb-48bb-a663-98ec4b5a96ed</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>6f5042e4-8e92-4267-8d5e-9039bd5ffdbe</t>
+          <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>1~2</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1 ~2</t>
+          <t>1 ~2 ,3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>G-Clef - Gut Punch</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>G-Clef - Gut Punch</t>
+          <t>G-Clef - Gut Punch – Low Kick</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1 1</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0 -15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0 -15</t>
+          <t>0 -15 -17</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+6 +5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>+6 +5</t>
+          <t>+6 +5 -3</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>+6 +5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>+6 +5</t>
+          <t>+6 +5 -3</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>5,8</t>
+          <t>5,8,10</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>hm</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>hm</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Damage of the 1st punch is only 5 if the 2nd punch isn't executed.</t>
+          <t>hmL</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
+          <t>eea0f2f5-415d-4625-b39b-23047f52db49</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>3c8fe17b-396a-488a-a85f-f6d1acec196d</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
           <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>93869afa-9cfe-4d58-ac4e-9f08aa9a710d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>– ~1</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 ~2 ~1</t>
+          <t>1 ~2 ,4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>– Skyscraper Cannon</t>
+          <t>– High Kick</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>G-Clef - Gut Punch – Skyscraper Cannon</t>
+          <t>G-Clef - Gut Punch – High Kick</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4786,69 +4876,69 @@
           <t>8</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0 -15</t>
+          <t>0 -15 -7</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>-7</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>+6 +5</t>
+          <t>+6 +5 -7</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>+6 +5</t>
+          <t>+6 +5 KD</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>5,8,21</t>
+          <t>5,8,20</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>hmm</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>The 3rd only occurs if the 1st hit was a counter hit. Second hit will be 15 damage.</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>hmh</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>f0f2bfda-dfa5-40f3-ae66-b166200ab547</t>
+          <t>5e4f379b-fd36-4665-83c6-0a7d14eaeba8</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>5748a150-d4fb-48bb-a663-98ec4b5a96ed</t>
+          <t>e175c8a1-2fcf-4f30-ae5e-0c4b8bcc5292</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -4860,62 +4950,47 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>f,f+1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1 ~2 ,3</t>
+          <t>f,f+1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>Party Crasher</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>G-Clef - Gut Punch – Low Kick</t>
+          <t>Party Crasher</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0 -15 -17</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>+6 +5 -3</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>+6 +5 -3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4930,37 +5005,27 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>5,8,10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>hmL</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>m</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>eea0f2f5-415d-4625-b39b-23047f52db49</t>
+          <t>23604313-0807-4e0f-a7dd-2c0696a15708</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>3c8fe17b-396a-488a-a85f-f6d1acec196d</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
+          <t>617ebe68-c949-400b-81d8-85f59e446512</t>
         </is>
       </c>
     </row>
@@ -4972,47 +5037,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1 ~2 ,4</t>
+          <t>f,f+1 ,4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>– High Kick</t>
+          <t>– Skyscraper Kick</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>G-Clef - Gut Punch – High Kick</t>
+          <t>Party Crasher – Skyscraper Kick</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0 -15 -7</t>
+          <t>-2 -11</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>+6 +5 -7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5022,69 +5087,74 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>+6 +5 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>5,8,20</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>hmh</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>5e4f379b-fd36-4665-83c6-0a7d14eaeba8</t>
+          <t>ac6252ff-738b-45cf-8214-59a0c37c6bb9</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>e175c8a1-2fcf-4f30-ae5e-0c4b8bcc5292</t>
+          <t>843b60ee-5df5-4ab3-84db-e8eeafa986f1</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>6f3db68f-f7e3-4d29-aa20-fddf7ac8ab21</t>
+          <t>23604313-0807-4e0f-a7dd-2c0696a15708</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>f,f+1</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>f,f+1</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Party Crasher</t>
+          <t>Pusher</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Party Crasher</t>
+          <t>Pusher</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5094,37 +5164,57 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -5139,34 +5229,34 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>23604313-0807-4e0f-a7dd-2c0696a15708</t>
+          <t>fc206d44-cab0-4658-a3ea-a475200d4790</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>617ebe68-c949-400b-81d8-85f59e446512</t>
+          <t>de1ebccf-5ffe-4cc0-91c2-e18e22c1748a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>1+4,3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>f,f+1 ,4</t>
+          <t>1+4 ,3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>– Skyscraper Kick</t>
+          <t>Club Fist - Bow &amp; Arrow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Party Crasher – Skyscraper Kick</t>
+          <t>Club Fist - Bow &amp; Arrow</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5174,106 +5264,101 @@
           <t>1 1</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20 x x</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20 x x</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>x -13 -12</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-2 -11</t>
+          <t>x -13 -12</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x -2 KD</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x -2 KD</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x -2 KD</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x -2 KD</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12,12,15</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>39</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>12,12,15</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mLm</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>mLm</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>ac6252ff-738b-45cf-8214-59a0c37c6bb9</t>
+          <t>f8532bb5-92b1-4c79-ace5-f60ecd8ba147</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>843b60ee-5df5-4ab3-84db-e8eeafa986f1</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>23604313-0807-4e0f-a7dd-2c0696a15708</t>
+          <t>e0af4fa2-4df5-418b-8873-74301385876f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>df+2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SS+1</t>
+          <t>df+2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pusher</t>
+          <t>Gut Punch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pusher</t>
+          <t>Gut Punch</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5283,57 +5368,57 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -5348,34 +5433,34 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>fc206d44-cab0-4658-a3ea-a475200d4790</t>
+          <t>660febf4-407c-4515-8a00-893c6e865407</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>de1ebccf-5ffe-4cc0-91c2-e18e22c1748a</t>
+          <t>be76ff29-47a8-439b-8fb9-996d53c57fba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>1+4,3</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1+4 ,3</t>
+          <t>df+2 ,1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Fist - Bow &amp; Arrow</t>
+          <t>– Skyscraper Cannon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Club Fist - Bow &amp; Arrow</t>
+          <t>Gut Punch – Skyscraper Cannon</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5383,146 +5468,141 @@
           <t>1 1</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20 x x</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>20 x x</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>x -13 -12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>x -13 -12</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>x -2 KD</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>x -2 KD</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>x -2 KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>x -2 KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>12,12,15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>12,12,15</t>
+          <t>10,21</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>mLm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>mLm</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>In the d/f+2,1 string the damage of the d/f+2 is 15. And has to hit from the front to work.</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>f8532bb5-92b1-4c79-ace5-f60ecd8ba147</t>
+          <t>f6d1c15e-318b-4d1b-aa4a-cdda0a81c936</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>e0af4fa2-4df5-418b-8873-74301385876f</t>
+          <t>9b9cf09b-7031-473b-8cc5-2134ac0c7650</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>660febf4-407c-4515-8a00-893c6e865407</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>df+2</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>df+2</t>
+          <t>df+2 ,3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gut Punch</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gut Punch</t>
+          <t>Gut Punch – Low Kick</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-6 -17</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+5 -3</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+5 -3</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5537,49 +5617,59 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10,10</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
+          <t>2d24d3a4-3fbf-489e-946b-372cd70d2695</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>addf3734-8445-428d-a7e3-f8992a5672c7</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
           <t>660febf4-407c-4515-8a00-893c6e865407</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>be76ff29-47a8-439b-8fb9-996d53c57fba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>df+2 ,1</t>
+          <t>df+2 ,4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>– Skyscraper Cannon</t>
+          <t>– High Kick</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gut Punch – Skyscraper Cannon</t>
+          <t>Gut Punch – High Kick</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5592,69 +5682,69 @@
           <t>16</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-6 -7</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>-7</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+5 -7</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>-7</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+5 -7</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>10,21</t>
+          <t>10,20</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>In the d/f+2,1 string the damage of the d/f+2 is 15. And has to hit from the front to work.</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>f6d1c15e-318b-4d1b-aa4a-cdda0a81c936</t>
+          <t>26065c0d-b052-4723-bbc4-cd6e91cac2ea</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>9b9cf09b-7031-473b-8cc5-2134ac0c7650</t>
+          <t>90f0c93e-2635-4dd7-85de-7c9e7235db55</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -5666,184 +5756,199 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>d+2~N+3,1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>df+2 ,3</t>
+          <t>d+2 ~N+3 ,1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2+3,1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>Ultimate Cannon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gut Punch – Low Kick</t>
+          <t>Ultimate Cannon</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 1 1</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10 x x</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10 x x</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>x -11 -8</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-6 -17</t>
+          <t>x -11 -8</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>x 0 KD</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>+5 -3</t>
+          <t>x 0 KD</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>x 0 KD</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>+5 -3</t>
+          <t>x 0 KD</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>(9,10_8,9) ,25</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>(9,10_8,9) ,25</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10,10</t>
+          <t>(9,10_8,9) ,25</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Smm</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>Smm</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2d24d3a4-3fbf-489e-946b-372cd70d2695</t>
+          <t>8a215398-0f57-4a39-9571-610535427a9a</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>addf3734-8445-428d-a7e3-f8992a5672c7</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>660febf4-407c-4515-8a00-893c6e865407</t>
+          <t>c6169995-1ea9-4ac8-b0f4-ad1d786a2576</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>df+2 ,4</t>
+          <t>f,f+2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>– High Kick</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gut Punch – High Kick</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-6 -7</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>+5 -7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>+5 -7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>10,20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -5853,161 +5958,146 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>26065c0d-b052-4723-bbc4-cd6e91cac2ea</t>
+          <t>a808579c-0674-4bdb-b65f-9096ce4b6758</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>90f0c93e-2635-4dd7-85de-7c9e7235db55</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>660febf4-407c-4515-8a00-893c6e865407</t>
+          <t>c1dd9a34-d556-4a34-ac56-15bd884a77c0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>d+2~N+3,1</t>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>d+2 ~N+3 ,1</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2+3,1</t>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ultimate Cannon</t>
+          <t>Flash Elbow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ultimate Cannon</t>
+          <t>Flash Elbow</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10 x x</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>10 x x</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>x -11 -8</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>x -11 -8</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>x 0 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>x 0 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>x 0 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>x 0 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>(9,10_8,9) ,25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>(9,10_8,9) ,25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>(9,10_8,9) ,25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Smm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Smm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>FSc</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>8a215398-0f57-4a39-9571-610535427a9a</t>
+          <t>87f85a0a-7f51-44f3-b998-581d928eeba1</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>c6169995-1ea9-4ac8-b0f4-ad1d786a2576</t>
+          <t>ce656918-6b00-4c70-8e77-af065888dd3c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>d,DF+2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>f,f+2</t>
+          <t>d,DF+2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Flash Arrow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Flash Arrow</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6017,99 +6107,104 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>FSc</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>a808579c-0674-4bdb-b65f-9096ce4b6758</t>
+          <t>edc9a051-b046-434a-835f-9467782d9d59</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>c1dd9a34-d556-4a34-ac56-15bd884a77c0</t>
+          <t>8d37e67b-149f-4d33-b868-666825292756</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>FC+df+2</t>
+          <t>SS+2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FC+df+2</t>
+          <t>SS+2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Flash Elbow</t>
+          <t>Snake Step</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Flash Elbow</t>
+          <t>Snake Step</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6119,139 +6214,139 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>FSc</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>87f85a0a-7f51-44f3-b998-581d928eeba1</t>
+          <t>2a148049-2090-4522-839b-231b42e377b2</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>ce656918-6b00-4c70-8e77-af065888dd3c</t>
+          <t>9d2e08d7-7a85-4416-bea2-6deee558f452</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>d,DF+2</t>
+          <t>SS+2~1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>d,DF+2</t>
+          <t>SS+2 ~1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Flash Arrow</t>
+          <t>Inner Palm Crush</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Flash Arrow</t>
+          <t>Inner Palm Crush</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6266,17 +6361,17 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -6289,41 +6384,41 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>FSc</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>edc9a051-b046-434a-835f-9467782d9d59</t>
+          <t>38a980c2-e824-4483-a085-22f60e0f1f94</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>8d37e67b-149f-4d33-b868-666825292756</t>
+          <t>40324b95-4f78-4bde-bc38-fc6694dbce1f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>SS+2</t>
+          <t>b+2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SS+2</t>
+          <t>b+2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2~b</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Snake Step</t>
+          <t>Arm Whip</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Snake Step</t>
+          <t>Arm Whip</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6333,42 +6428,42 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6388,49 +6483,54 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>The Arm Whip needs to hit for Michelle to spin around the opponent.</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2a148049-2090-4522-839b-231b42e377b2</t>
+          <t>65aaecf4-ea4f-4d97-b0ed-4df6be392720</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>9d2e08d7-7a85-4416-bea2-6deee558f452</t>
+          <t>658a2394-ca26-4994-a95e-31cfe4fd82b7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>SS+2~1</t>
+          <t>– 1+2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SS+2 ~1</t>
+          <t>b+2 ,1+2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Inner Palm Crush</t>
+          <t>– Back Push</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Inner Palm Crush</t>
+          <t>Arm Whip – Back Push</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6438,218 +6538,173 @@
           <t>1 1</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-2 +2</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-1 +2</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-1 +2</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12,-</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h-</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>38a980c2-e824-4483-a085-22f60e0f1f94</t>
+          <t>8045d9f7-3789-4f1b-b9c6-3335bf7f87f4</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>40324b95-4f78-4bde-bc38-fc6694dbce1f</t>
+          <t>3c2c5a63-03b4-44d5-ab93-663e488b4621</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>65aaecf4-ea4f-4d97-b0ed-4df6be392720</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>b+2</t>
+          <t>– d+1+2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>b+2</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2~b</t>
+          <t>b+2 ,d+1+2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arm Whip</t>
+          <t>– Rear Suplex</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arm Whip</t>
+          <t>Arm Whip – Rear Suplex</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12,45</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>OB</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>The Arm Whip needs to hit for Michelle to spin around the opponent.</t>
+          <t>h!</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
+          <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>f1c6a2cd-8f86-45e2-8020-1482f8fb6c52</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
           <t>65aaecf4-ea4f-4d97-b0ed-4df6be392720</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>658a2394-ca26-4994-a95e-31cfe4fd82b7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>– 1+2</t>
+          <t>– 5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>b+2 ,1+2</t>
+          <t>b+2 ,5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>– Back Push</t>
+          <t>– Back Push into Julia's Running Bulldog</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arm Whip – Back Push</t>
+          <t>Arm Whip – Back Push into Julia's Running Bulldog</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6662,74 +6717,44 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>-2 +2</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>-1 +2</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>-1 +2</t>
-        </is>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>12,-</t>
+          <t>12,24</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>!</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>h-</t>
+          <t>h!</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>Causes Special Tag Throw with Julia, see the Grappling Arts.</t>
+          <t>Only with Julia.</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>8045d9f7-3789-4f1b-b9c6-3335bf7f87f4</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>3c2c5a63-03b4-44d5-ab93-663e488b4621</t>
+          <t>1929ca31-425b-4548-b294-f29693b8fe20</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -9562,6 +9587,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
+        </is>
+      </c>
       <c r="AB100" t="inlineStr">
         <is>
           <t>0fc0ca0b-d962-4684-9515-834d1e1283b6</t>
@@ -9614,6 +9644,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
+        </is>
+      </c>
       <c r="AB101" t="inlineStr">
         <is>
           <t>b5de5a0d-851a-4ca2-ad04-246afb578ddb</t>
@@ -9664,6 +9699,11 @@
       <c r="U102" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>04575a0d-bb87-4254-a98a-681589f81afc</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
